--- a/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-49770</t>
+          <t>I-49883</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.2333927</t>
+          <t>-6.22997</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.867265</t>
+          <t>-77.8753642</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hermosura / Sociego</t>
+          <t>Jirón Puno / Jirón Amazonas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-488744</t>
+          <t>I-49770</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.234945</t>
+          <t>-6.2333927</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-77.868379</t>
+          <t>-77.867265</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INTERSECCION Jr. TRES ESQUINAS CON Jr. LOS ÁNGELES</t>
+          <t>Hermosura / Sociego</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-49875</t>
+          <t>I-49875</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INTERSECCION Jr. SANTA ANA CON Jr. HERMOSURA</t>
+          <t>Calle Santa Ana / Calle Hermosura</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-49924</t>
+          <t>I-49924</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>INTERSECCION Jr. DOS DE MAYO CON Jr. AYACUCHO</t>
+          <t>Jirón Dos de Mayo / Jirón Ayacucho</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -683,6 +683,162 @@
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-49805</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-6.2355541</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-77.8710872</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2 de Mayo / Jirón Dos de Mayo / Jirón Grau</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-49813</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-6.2306939</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-77.8718798</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Jirón Grau / Jirón Triunfo</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-49918</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-6.2323878</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-77.8709348</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jirón Dos de Mayo / Jirón Piura</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>010101</t>
         </is>

--- a/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón Puno / Jirón Amazonas</t>
+          <t>Jirón Amazonas / Jirón Puno</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle Santa Ana / Calle Hermosura</t>
+          <t>Hermosura / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jirón Dos de Mayo / Jirón Ayacucho</t>
+          <t>Jirón Ayacucho / Jirón Dos de Mayo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-49883</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>010101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-6.22997</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>010101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-49770</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>010101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-6.2333927</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>010101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-49875</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>010101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-6.226347</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>010101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-49924</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>010101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-6.228983</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>010101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-49805</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>010101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-6.2355541</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>010101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-49813</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>010101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-6.2306939</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>010101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CHACHAPOYAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-49918</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>010101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CHACHAPOYAS</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-6.2323878</t>
@@ -836,11 +801,6 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>010101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/Intersecciones/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-49883</t>
+          <t>I-49924</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.22997</t>
+          <t>-6.228983</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-77.8753642</t>
+          <t>-77.870993</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón Amazonas / Jirón Puno</t>
+          <t>Jirón Dos de Mayo / Jirón Ayacucho</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-49770</t>
+          <t>I-49918</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.2333927</t>
+          <t>-6.2323878</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-77.867265</t>
+          <t>-77.8709348</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hermosura / Sociego</t>
+          <t>Jirón Dos de Mayo / Jirón Piura</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-49875</t>
+          <t>I-49883</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.226347</t>
+          <t>-6.22997</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-77.867502</t>
+          <t>-77.8753642</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hermosura / Calle s / n</t>
+          <t>Jirón Puno / Jirón Amazonas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-49924</t>
+          <t>I-49875</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.228983</t>
+          <t>-6.226347</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-77.870993</t>
+          <t>-77.867502</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jirón Ayacucho / Jirón Dos de Mayo</t>
+          <t>Calle Santa Ana / Calle Hermosura</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-49805</t>
+          <t>I-49813</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.2355541</t>
+          <t>-6.2306939</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-77.8710872</t>
+          <t>-77.8718798</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2 de Mayo / Jirón Dos de Mayo / Jirón Grau</t>
+          <t>Jirón Grau / Jirón Triunfo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-49813</t>
+          <t>I-49805</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.2306939</t>
+          <t>-6.2355541</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-77.8718798</t>
+          <t>-77.8710872</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jirón Grau / Jirón Triunfo</t>
+          <t>2 de Mayo / Jirón Dos de Mayo / Jirón Grau</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-49918</t>
+          <t>I-49770</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.2323878</t>
+          <t>-6.2333927</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-77.8709348</t>
+          <t>-77.867265</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jirón Dos de Mayo / Jirón Piura</t>
+          <t>Hermosura / Sociego</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
